--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F15" s="14">
-        <v>5</v>
-      </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>16.666666666666</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="M15" s="15">
         <v>75</v>
       </c>
       <c r="N15" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-42.857142857142</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H16" s="15">
-        <v>-41.176470588235</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="I16" s="14">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K16" s="15">
-        <v>-42</v>
+        <v>-35.593220338983</v>
       </c>
       <c r="L16" s="15">
-        <v>-40.816326530612</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.705882352941</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.255924170616</v>
+        <v>-84.980237154150</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-61.904761904761</v>
+        <v>88.888888888888</v>
       </c>
       <c r="F17" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G17" s="14">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.017543859649</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K17" s="15">
-        <v>2.898550724637</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>14.516129032258</v>
+        <v>15.189873417721</v>
       </c>
       <c r="M17" s="15">
-        <v>54.347826086956</v>
+        <v>65.454545454545</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.390804597701</v>
+        <v>-8.080808080808</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
         <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>-58.974358974359</v>
+        <v>-56.818181818181</v>
       </c>
       <c r="L18" s="15">
-        <v>-54.285714285714</v>
+        <v>-53.658536585365</v>
       </c>
       <c r="M18" s="15">
-        <v>-65.217391304347</v>
+        <v>-63.461538461538</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.542483660130</v>
+        <v>-89.204545454545</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E19" s="15">
-        <v>-29.411764705882</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H19" s="15">
-        <v>-33.75</v>
+        <v>-35.802469135802</v>
       </c>
       <c r="I19" s="14">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="J19" s="14">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.618556701030</v>
+        <v>-21.008403361344</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.357798165137</v>
+        <v>-26.5625</v>
       </c>
       <c r="M19" s="15">
-        <v>50.980392156862</v>
+        <v>67.857142857142</v>
       </c>
       <c r="N19" s="15">
-        <v>22.222222222222</v>
+        <v>32.394366197183</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15">
-        <v>11.111111111111</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="F20" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G20" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H20" s="15">
-        <v>22.580645161290</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="I20" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J20" s="14">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="K20" s="15">
-        <v>2.173913043478</v>
+        <v>-13.559322033898</v>
       </c>
       <c r="L20" s="15">
-        <v>-7.843137254901</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M20" s="15">
-        <v>147.368421052632</v>
+        <v>112.5</v>
       </c>
       <c r="N20" s="15">
-        <v>-80</v>
+        <v>-81.040892193308</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.870967741935</v>
+        <v>-19.672131147541</v>
       </c>
       <c r="F21" s="17">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G21" s="17">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.222222222222</v>
+        <v>-25.833333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="J21" s="17">
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.064724919093</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.064724919093</v>
+        <v>-19.571045576407</v>
       </c>
       <c r="M21" s="18">
-        <v>23.5</v>
+        <v>27.659574468085</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.712418300653</v>
+        <v>-66.178128523111</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="14">
         <v>3</v>
       </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
-      <c r="H22" s="15">
-        <v>50</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="F23" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H23" s="15">
         <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J23" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K23" s="15">
-        <v>4.761904761904</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.666666666666</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="M23" s="15">
-        <v>37.5</v>
+        <v>26.086956521739</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E24" s="15">
-        <v>-21.875</v>
+        <v>-56.363636363636</v>
       </c>
       <c r="F24" s="14">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G24" s="14">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.382165605095</v>
+        <v>-31.547619047619</v>
       </c>
       <c r="I24" s="14">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="J24" s="14">
-        <v>209</v>
+        <v>264</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.612440191387</v>
+        <v>-18.939393939393</v>
       </c>
       <c r="L24" s="15">
-        <v>2.139037433155</v>
+        <v>-0.925925925925</v>
       </c>
       <c r="M24" s="15">
-        <v>32.638888888888</v>
+        <v>30.487804878048</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>-85.714285714285</v>
+        <v>-78.260869565217</v>
       </c>
       <c r="F25" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G25" s="14">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.297872340425</v>
+        <v>-52.542372881355</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J25" s="14">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="K25" s="15">
-        <v>-37.704918032786</v>
+        <v>-48.809523809523</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.538461538461</v>
+        <v>-41.095890410958</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>-5.263157894736</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G26" s="14">
         <v>57</v>
       </c>
       <c r="H26" s="15">
-        <v>42.105263157894</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I26" s="14">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="J26" s="14">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="K26" s="15">
-        <v>25.555555555555</v>
+        <v>20.952380952381</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.377049180327</v>
+        <v>-14.189189189189</v>
       </c>
       <c r="M26" s="15">
-        <v>-26.143790849673</v>
+        <v>-28.248587570621</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="I27" s="14">
+        <v>9</v>
+      </c>
+      <c r="J27" s="14">
+        <v>9</v>
+      </c>
+      <c r="K27" s="15">
         <v>0</v>
       </c>
-      <c r="I27" s="14">
-        <v>8</v>
-      </c>
-      <c r="J27" s="14">
-        <v>6</v>
-      </c>
-      <c r="K27" s="15">
-        <v>33.333333333333</v>
-      </c>
       <c r="L27" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>-64.285714285714</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+        <v>-80</v>
+      </c>
+      <c r="M29" s="15">
+        <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+        <v>-80</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -878,8 +878,8 @@
       <c r="K14" s="15">
         <v>-100</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>-100</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>-71.428571428571</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-22.222222222222</v>
+        <v>-10</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="M15" s="15">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="N15" s="15">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-11.111111111111</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>-32.432432432432</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.593220338983</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.923076923076</v>
+        <v>-27.868852459016</v>
       </c>
       <c r="M16" s="15">
-        <v>-13.636363636363</v>
+        <v>-22.807017543859</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.980237154150</v>
+        <v>-85.084745762711</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>88.888888888888</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="J17" s="14">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K17" s="15">
-        <v>16.666666666666</v>
+        <v>16.129032258064</v>
       </c>
       <c r="L17" s="15">
-        <v>15.189873417721</v>
+        <v>21.348314606741</v>
       </c>
       <c r="M17" s="15">
-        <v>65.454545454545</v>
+        <v>66.153846153846</v>
       </c>
       <c r="N17" s="15">
-        <v>-8.080808080808</v>
+        <v>-3.571428571428</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
         <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-45.833333333333</v>
+        <v>-35</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K18" s="15">
-        <v>-56.818181818181</v>
+        <v>-55.102040816326</v>
       </c>
       <c r="L18" s="15">
-        <v>-53.658536585365</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.461538461538</v>
+        <v>-62.711864406779</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.204545454545</v>
+        <v>-88.775510204081</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.727272727272</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H19" s="15">
-        <v>-35.802469135802</v>
+        <v>-40</v>
       </c>
       <c r="I19" s="14">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J19" s="14">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="K19" s="15">
-        <v>-21.008403361344</v>
+        <v>-28.082191780821</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.5625</v>
+        <v>-22.794117647058</v>
       </c>
       <c r="M19" s="15">
-        <v>67.857142857142</v>
+        <v>50</v>
       </c>
       <c r="N19" s="15">
-        <v>32.394366197183</v>
+        <v>15.384615384615</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-69.230769230769</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
         <v>36</v>
       </c>
       <c r="H20" s="15">
-        <v>-13.888888888888</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J20" s="14">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.559322033898</v>
+        <v>-19.117647058823</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.086956521739</v>
+        <v>-24.657534246575</v>
       </c>
       <c r="M20" s="15">
-        <v>112.5</v>
+        <v>89.655172413793</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.040892193308</v>
+        <v>-81.788079470198</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E21" s="18">
-        <v>-19.672131147541</v>
+        <v>-40.625</v>
       </c>
       <c r="F21" s="17">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="G21" s="17">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.833333333333</v>
+        <v>-27.155172413793</v>
       </c>
       <c r="I21" s="17">
-        <v>300</v>
+        <v>343</v>
       </c>
       <c r="J21" s="17">
-        <v>370</v>
+        <v>434</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.918918918918</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.571045576407</v>
+        <v>-17.548076923076</v>
       </c>
       <c r="M21" s="18">
-        <v>27.659574468085</v>
+        <v>20.774647887323</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.178128523111</v>
+        <v>-66.339548577036</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="14">
         <v>7</v>
       </c>
-      <c r="D23" s="14">
-        <v>5</v>
-      </c>
       <c r="E23" s="15">
-        <v>40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G23" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H23" s="15">
+        <v>-29.166666666666</v>
+      </c>
+      <c r="I23" s="14">
+        <v>33</v>
+      </c>
+      <c r="J23" s="14">
+        <v>33</v>
+      </c>
+      <c r="K23" s="15">
         <v>0</v>
       </c>
-      <c r="I23" s="14">
-        <v>29</v>
-      </c>
-      <c r="J23" s="14">
-        <v>26</v>
-      </c>
-      <c r="K23" s="15">
-        <v>11.538461538461</v>
-      </c>
       <c r="L23" s="15">
-        <v>-23.684210526315</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M23" s="15">
-        <v>26.086956521739</v>
+        <v>10</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
         <v>55</v>
       </c>
       <c r="E24" s="15">
-        <v>-56.363636363636</v>
+        <v>-47.272727272727</v>
       </c>
       <c r="F24" s="14">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G24" s="14">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="H24" s="15">
-        <v>-31.547619047619</v>
+        <v>-37.912087912087</v>
       </c>
       <c r="I24" s="14">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="J24" s="14">
-        <v>264</v>
+        <v>319</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.939393939393</v>
+        <v>-23.824451410658</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.925925925925</v>
+        <v>-1.619433198380</v>
       </c>
       <c r="M24" s="15">
-        <v>30.487804878048</v>
+        <v>26.5625</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E25" s="15">
-        <v>-78.260869565217</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H25" s="15">
-        <v>-52.542372881355</v>
+        <v>-60.294117647058</v>
       </c>
       <c r="I25" s="14">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="J25" s="14">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="K25" s="15">
-        <v>-48.809523809523</v>
+        <v>-50.458715596330</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.095890410958</v>
+        <v>-34.939759036144</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>18</v>
+      </c>
+      <c r="D26" s="14">
         <v>16</v>
       </c>
-      <c r="D26" s="14">
-        <v>15</v>
-      </c>
       <c r="E26" s="15">
-        <v>6.666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G26" s="14">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H26" s="15">
-        <v>21.052631578947</v>
+        <v>14.545454545454</v>
       </c>
       <c r="I26" s="14">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="J26" s="14">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="K26" s="15">
-        <v>20.952380952381</v>
+        <v>16.528925619834</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.189189189189</v>
+        <v>-18.023255813953</v>
       </c>
       <c r="M26" s="15">
-        <v>-28.248587570621</v>
+        <v>-30.882352941176</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-57.142857142857</v>
+        <v>-37.5</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>66.666666666666</v>
+        <v>400</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>4</v>
       </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="L28" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,23 +1466,23 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1500,30 +1500,30 @@
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.736842105263</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.736842105263</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-42.857142857142</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
         <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="L15" s="15">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="M15" s="15">
-        <v>125</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-25</v>
+        <v>-8.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>-14.285714285714</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
         <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-22.580645161290</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.526315789473</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.868852459016</v>
+        <v>-32.876712328767</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.807017543859</v>
+        <v>-19.672131147541</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.084745762711</v>
+        <v>-85.416666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>-6.666666666666</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F17" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G17" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.448275862068</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="I17" s="14">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="J17" s="14">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="K17" s="15">
-        <v>16.129032258064</v>
+        <v>12.612612612612</v>
       </c>
       <c r="L17" s="15">
-        <v>21.348314606741</v>
+        <v>26.262626262626</v>
       </c>
       <c r="M17" s="15">
-        <v>66.153846153846</v>
+        <v>60.256410256410</v>
       </c>
       <c r="N17" s="15">
-        <v>-3.571428571428</v>
+        <v>-1.574803149606</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>20</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-35</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K18" s="15">
-        <v>-55.102040816326</v>
+        <v>-46.296296296296</v>
       </c>
       <c r="L18" s="15">
-        <v>-57.692307692307</v>
+        <v>-49.122807017543</v>
       </c>
       <c r="M18" s="15">
-        <v>-62.711864406779</v>
+        <v>-56.716417910447</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.775510204081</v>
+        <v>-87.336244541484</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" s="15">
-        <v>-55.555555555555</v>
+        <v>-52</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G19" s="14">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H19" s="15">
-        <v>-40</v>
+        <v>-43.956043956044</v>
       </c>
       <c r="I19" s="14">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="J19" s="14">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="K19" s="15">
-        <v>-28.082191780821</v>
+        <v>-30.994152046783</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.794117647058</v>
+        <v>-24.840764331210</v>
       </c>
       <c r="M19" s="15">
-        <v>50</v>
+        <v>51.282051282051</v>
       </c>
       <c r="N19" s="15">
-        <v>15.384615384615</v>
+        <v>9.259259259259</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
         <v>36</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="I20" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J20" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K20" s="15">
-        <v>-19.117647058823</v>
+        <v>-17.808219178082</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.657534246575</v>
+        <v>-22.077922077922</v>
       </c>
       <c r="M20" s="15">
-        <v>89.655172413793</v>
+        <v>76.470588235294</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.788079470198</v>
+        <v>-82.035928143712</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" s="18">
-        <v>-40.625</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="G21" s="17">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.155172413793</v>
+        <v>-27.6</v>
       </c>
       <c r="I21" s="17">
-        <v>343</v>
+        <v>392</v>
       </c>
       <c r="J21" s="17">
-        <v>434</v>
+        <v>497</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.967741935483</v>
+        <v>-21.126760563380</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.548076923076</v>
+        <v>-16.239316239316</v>
       </c>
       <c r="M21" s="18">
-        <v>20.774647887323</v>
+        <v>20.987654320987</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.339548577036</v>
+        <v>-66.119273984442</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F22" s="14">
-        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
         <v>17</v>
       </c>
       <c r="G23" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H23" s="15">
-        <v>-29.166666666666</v>
+        <v>-15</v>
       </c>
       <c r="I23" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J23" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>2.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>-15.384615384615</v>
+        <v>-20</v>
       </c>
       <c r="M23" s="15">
-        <v>10</v>
+        <v>16.129032258064</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E24" s="15">
-        <v>-47.272727272727</v>
+        <v>-50</v>
       </c>
       <c r="F24" s="14">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G24" s="14">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="H24" s="15">
-        <v>-37.912087912087</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="I24" s="14">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="J24" s="14">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.824451410658</v>
+        <v>-27.345844504021</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.619433198380</v>
+        <v>-6.228373702422</v>
       </c>
       <c r="M24" s="15">
-        <v>26.5625</v>
+        <v>27.230046948356</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>-65.384615384615</v>
       </c>
       <c r="F25" s="14">
         <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="H25" s="15">
-        <v>-60.294117647058</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="J25" s="14">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="K25" s="15">
-        <v>-50.458715596330</v>
+        <v>-52.592592592592</v>
       </c>
       <c r="L25" s="15">
-        <v>-34.939759036144</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>13</v>
+      </c>
+      <c r="D26" s="14">
         <v>18</v>
       </c>
-      <c r="D26" s="14">
-        <v>16</v>
-      </c>
       <c r="E26" s="15">
-        <v>12.5</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F26" s="14">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G26" s="14">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H26" s="15">
-        <v>14.545454545454</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="I26" s="14">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J26" s="14">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="K26" s="15">
-        <v>16.528925619834</v>
+        <v>10.791366906474</v>
       </c>
       <c r="L26" s="15">
-        <v>-18.023255813953</v>
+        <v>-22.613065326633</v>
       </c>
       <c r="M26" s="15">
-        <v>-30.882352941176</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-37.5</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>83.333333333333</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
+        <v>2</v>
+      </c>
+      <c r="H28" s="15">
+        <v>200</v>
+      </c>
+      <c r="I28" s="14">
+        <v>10</v>
+      </c>
+      <c r="J28" s="14">
         <v>5</v>
       </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
-      <c r="H28" s="15">
-        <v>400</v>
-      </c>
-      <c r="I28" s="14">
-        <v>9</v>
-      </c>
-      <c r="J28" s="14">
-        <v>4</v>
-      </c>
       <c r="K28" s="15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,90 +1466,90 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M29" s="15">
         <v>0</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.238095238095</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M30" s="15">
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.736842105263</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1610,17 +1610,17 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1629,7 +1629,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
+      <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H15" s="15">
-        <v>-16.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="I15" s="14">
         <v>11</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>10</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L15" s="15">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="M15" s="15">
         <v>83.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-8.333333333333</v>
+        <v>-21.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>10</v>
-      </c>
       <c r="E16" s="15">
-        <v>-60</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H16" s="15">
-        <v>-27.272727272727</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J16" s="14">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.526315789473</v>
+        <v>-33.75</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.876712328767</v>
+        <v>-41.758241758241</v>
       </c>
       <c r="M16" s="15">
-        <v>-19.672131147541</v>
+        <v>-27.397260273972</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.416666666666</v>
+        <v>-85.941644562334</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-5.555555555555</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G17" s="14">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H17" s="15">
-        <v>-4.761904761904</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I17" s="14">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J17" s="14">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="K17" s="15">
-        <v>12.612612612612</v>
+        <v>8.661417322834</v>
       </c>
       <c r="L17" s="15">
-        <v>26.262626262626</v>
+        <v>22.123893805309</v>
       </c>
       <c r="M17" s="15">
-        <v>60.256410256410</v>
+        <v>45.263157894736</v>
       </c>
       <c r="N17" s="15">
-        <v>-1.574803149606</v>
+        <v>-2.816901408450</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-9.523809523809</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J18" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.296296296296</v>
+        <v>-43.859649122807</v>
       </c>
       <c r="L18" s="15">
-        <v>-49.122807017543</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.716417910447</v>
+        <v>-57.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.336244541484</v>
+        <v>-88.489208633093</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15">
-        <v>-52</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H19" s="15">
-        <v>-43.956043956044</v>
+        <v>-47.872340425531</v>
       </c>
       <c r="I19" s="14">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="J19" s="14">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="K19" s="15">
-        <v>-30.994152046783</v>
+        <v>-32.984293193717</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.840764331210</v>
+        <v>-28.089887640449</v>
       </c>
       <c r="M19" s="15">
-        <v>51.282051282051</v>
+        <v>43.820224719101</v>
       </c>
       <c r="N19" s="15">
-        <v>9.259259259259</v>
+        <v>-1.538461538461</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F20" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H20" s="15">
-        <v>-38.888888888888</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="I20" s="14">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J20" s="14">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K20" s="15">
-        <v>-17.808219178082</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.077922077922</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="15">
-        <v>76.470588235294</v>
+        <v>89.473684210526</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.035928143712</v>
+        <v>-80.592991913746</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D21" s="17">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E21" s="18">
-        <v>-28.571428571428</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="F21" s="17">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G21" s="17">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.6</v>
+        <v>-28.048780487804</v>
       </c>
       <c r="I21" s="17">
-        <v>392</v>
+        <v>434</v>
       </c>
       <c r="J21" s="17">
-        <v>497</v>
+        <v>555</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.126760563380</v>
+        <v>-21.801801801801</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.239316239316</v>
+        <v>-20.220588235294</v>
       </c>
       <c r="M21" s="18">
-        <v>20.987654320987</v>
+        <v>15.425531914893</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.119273984442</v>
+        <v>-67.220543806646</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>25</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M22" s="15">
         <v>150</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>6</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
+        <v>19</v>
+      </c>
+      <c r="G23" s="14">
         <v>17</v>
       </c>
-      <c r="G23" s="14">
-        <v>20</v>
-      </c>
       <c r="H23" s="15">
-        <v>-15</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I23" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J23" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K23" s="15">
-        <v>2.857142857142</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L23" s="15">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="M23" s="15">
-        <v>16.129032258064</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="E24" s="15">
-        <v>-50</v>
+        <v>10.256410256410</v>
       </c>
       <c r="F24" s="14">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="G24" s="14">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H24" s="15">
-        <v>-46.428571428571</v>
+        <v>-38.423645320197</v>
       </c>
       <c r="I24" s="14">
-        <v>271</v>
+        <v>315</v>
       </c>
       <c r="J24" s="14">
-        <v>373</v>
+        <v>412</v>
       </c>
       <c r="K24" s="15">
-        <v>-27.345844504021</v>
+        <v>-23.543689320388</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.228373702422</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="M24" s="15">
-        <v>27.230046948356</v>
+        <v>38.157894736842</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-65.384615384615</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F25" s="14">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G25" s="14">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H25" s="15">
-        <v>-66.666666666666</v>
+        <v>-58.620689655172</v>
       </c>
       <c r="I25" s="14">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J25" s="14">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="K25" s="15">
-        <v>-52.592592592592</v>
+        <v>-50</v>
       </c>
       <c r="L25" s="15">
-        <v>-30.434782608695</v>
+        <v>-30.188679245283</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>-27.777777777777</v>
+        <v>26.315789473684</v>
       </c>
       <c r="F26" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G26" s="14">
         <v>68</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.294117647058</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="I26" s="14">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="J26" s="14">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="K26" s="15">
-        <v>10.791366906474</v>
+        <v>12.025316455696</v>
       </c>
       <c r="L26" s="15">
-        <v>-22.613065326633</v>
+        <v>-19.178082191780</v>
       </c>
       <c r="M26" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.588235294117</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
         <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>-6.25</v>
       </c>
       <c r="L27" s="15">
-        <v>150</v>
+        <v>87.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>-52.380952380952</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.476190476190</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,48 +1508,48 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="M30" s="15">
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.473684210526</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1610,17 +1610,17 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
@@ -905,28 +905,28 @@
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>11</v>
       </c>
       <c r="J15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>-21.428571428571</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>120</v>
       </c>
       <c r="M15" s="15">
-        <v>83.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N15" s="15">
-        <v>-21.428571428571</v>
+        <v>-26.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F16" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
         <v>30</v>
       </c>
       <c r="H16" s="15">
-        <v>-23.333333333333</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J16" s="14">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.75</v>
+        <v>-35.955056179775</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.758241758241</v>
+        <v>-41.836734693877</v>
       </c>
       <c r="M16" s="15">
-        <v>-27.397260273972</v>
+        <v>-33.720930232558</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.941644562334</v>
+        <v>-86.330935251798</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,31 +984,31 @@
         <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G17" s="14">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H17" s="15">
-        <v>6.896551724137</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I17" s="14">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="J17" s="14">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="K17" s="15">
-        <v>8.661417322834</v>
+        <v>5.594405594405</v>
       </c>
       <c r="L17" s="15">
-        <v>22.123893805309</v>
+        <v>17.96875</v>
       </c>
       <c r="M17" s="15">
-        <v>45.263157894736</v>
+        <v>49.504950495049</v>
       </c>
       <c r="N17" s="15">
-        <v>-2.816901408450</v>
+        <v>-3.821656050955</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
         <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-11.111111111111</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I18" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J18" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.859649122807</v>
+        <v>-43.548387096774</v>
       </c>
       <c r="L18" s="15">
-        <v>-51.515151515151</v>
+        <v>-51.388888888888</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.333333333333</v>
+        <v>-56.790123456790</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.489208633093</v>
+        <v>-88.958990536277</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G19" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H19" s="15">
-        <v>-47.872340425531</v>
+        <v>-48.484848484848</v>
       </c>
       <c r="I19" s="14">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="J19" s="14">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="K19" s="15">
-        <v>-32.984293193717</v>
+        <v>-33.486238532110</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.089887640449</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="M19" s="15">
-        <v>43.820224719101</v>
+        <v>45</v>
       </c>
       <c r="N19" s="15">
-        <v>-1.538461538461</v>
+        <v>-3.333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>9.090909090909</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G20" s="14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H20" s="15">
-        <v>-36.842105263157</v>
+        <v>-3.125</v>
       </c>
       <c r="I20" s="14">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="J20" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K20" s="15">
-        <v>-14.285714285714</v>
+        <v>-8.791208791208</v>
       </c>
       <c r="L20" s="15">
-        <v>-20</v>
+        <v>-15.306122448979</v>
       </c>
       <c r="M20" s="15">
-        <v>89.473684210526</v>
+        <v>93.023255813953</v>
       </c>
       <c r="N20" s="15">
-        <v>-80.592991913746</v>
+        <v>-79.040404040404</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D21" s="17">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E21" s="18">
-        <v>-31.034482758620</v>
+        <v>-29.230769230769</v>
       </c>
       <c r="F21" s="17">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G21" s="17">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.048780487804</v>
+        <v>-30.8</v>
       </c>
       <c r="I21" s="17">
-        <v>434</v>
+        <v>482</v>
       </c>
       <c r="J21" s="17">
-        <v>555</v>
+        <v>620</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.801801801801</v>
+        <v>-22.258064516129</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.220588235294</v>
+        <v>-18.581081081081</v>
       </c>
       <c r="M21" s="18">
-        <v>15.425531914893</v>
+        <v>15.311004784689</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.220543806646</v>
+        <v>-67.098976109215</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G23" s="14">
         <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>11.764705882352</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I23" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J23" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K23" s="15">
-        <v>10.526315789473</v>
+        <v>6.976744186046</v>
       </c>
       <c r="L23" s="15">
-        <v>-16</v>
+        <v>-16.363636363636</v>
       </c>
       <c r="M23" s="15">
-        <v>7.692307692307</v>
+        <v>9.523809523809</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D24" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>10.256410256410</v>
+        <v>29.729729729729</v>
       </c>
       <c r="F24" s="14">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G24" s="14">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H24" s="15">
-        <v>-38.423645320197</v>
+        <v>-19.459459459459</v>
       </c>
       <c r="I24" s="14">
-        <v>315</v>
+        <v>363</v>
       </c>
       <c r="J24" s="14">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.543689320388</v>
+        <v>-19.153674832962</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.777777777777</v>
+        <v>2.542372881355</v>
       </c>
       <c r="M24" s="15">
-        <v>38.157894736842</v>
+        <v>35.447761194029</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.076923076923</v>
+        <v>88.888888888888</v>
       </c>
       <c r="F25" s="14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G25" s="14">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H25" s="15">
-        <v>-58.620689655172</v>
+        <v>-36.986301369863</v>
       </c>
       <c r="I25" s="14">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J25" s="14">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="K25" s="15">
-        <v>-50</v>
+        <v>-42.675159235668</v>
       </c>
       <c r="L25" s="15">
-        <v>-30.188679245283</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E26" s="15">
-        <v>26.315789473684</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="F26" s="14">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G26" s="14">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.470588235294</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="J26" s="14">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="K26" s="15">
-        <v>12.025316455696</v>
+        <v>3.174603174603</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.178082191780</v>
+        <v>-20.081967213114</v>
       </c>
       <c r="M26" s="15">
-        <v>-30.588235294117</v>
+        <v>-32.055749128919</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,7 +1388,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
@@ -1397,22 +1397,22 @@
         <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>87.5</v>
+        <v>112.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>57.142857142857</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L28" s="15">
-        <v>-47.619047619047</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,13 +1476,13 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
@@ -1500,15 +1500,15 @@
         <v>-20</v>
       </c>
       <c r="N29" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>2</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,13 +1517,13 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,26 +1616,26 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="14">
         <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,26 +854,26 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -881,8 +881,8 @@
       <c r="L14" s="15">
         <v>-100</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -890,43 +890,43 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="E15" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
         <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>-26.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N15" s="15">
-        <v>-26.666666666666</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-77.777777777777</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H16" s="15">
-        <v>-36.666666666666</v>
+        <v>-46.875</v>
       </c>
       <c r="I16" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J16" s="14">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.955056179775</v>
+        <v>-36.734693877551</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.836734693877</v>
+        <v>-40.952380952380</v>
       </c>
       <c r="M16" s="15">
-        <v>-33.720930232558</v>
+        <v>-35.416666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.330935251798</v>
+        <v>-86.191536748329</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
         <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="14">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.384615384615</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I17" s="14">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="J17" s="14">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="K17" s="15">
-        <v>5.594405594405</v>
+        <v>2.515723270440</v>
       </c>
       <c r="L17" s="15">
-        <v>17.96875</v>
+        <v>15.602836879432</v>
       </c>
       <c r="M17" s="15">
-        <v>49.504950495049</v>
+        <v>40.517241379310</v>
       </c>
       <c r="N17" s="15">
-        <v>-3.821656050955</v>
+        <v>-4.117647058823</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
         <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.548387096774</v>
+        <v>-38.805970149253</v>
       </c>
       <c r="L18" s="15">
-        <v>-51.388888888888</v>
+        <v>-46.052631578947</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.790123456790</v>
+        <v>-52.325581395348</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.958990536277</v>
+        <v>-88.285714285714</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
         <v>27</v>
       </c>
       <c r="E19" s="15">
-        <v>-37.037037037037</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
         <v>99</v>
       </c>
       <c r="H19" s="15">
-        <v>-48.484848484848</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="I19" s="14">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="J19" s="14">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="K19" s="15">
-        <v>-33.486238532110</v>
+        <v>-33.469387755102</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.684210526315</v>
+        <v>-19.704433497536</v>
       </c>
       <c r="M19" s="15">
-        <v>45</v>
+        <v>53.773584905660</v>
       </c>
       <c r="N19" s="15">
-        <v>-3.333333333333</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
         <v>11</v>
       </c>
-      <c r="D20" s="14">
-        <v>7</v>
-      </c>
       <c r="E20" s="15">
-        <v>57.142857142857</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F20" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G20" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H20" s="15">
-        <v>-3.125</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I20" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J20" s="14">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="K20" s="15">
-        <v>-8.791208791208</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="L20" s="15">
-        <v>-15.306122448979</v>
+        <v>-17.924528301886</v>
       </c>
       <c r="M20" s="15">
-        <v>93.023255813953</v>
+        <v>97.727272727272</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.040404040404</v>
+        <v>-79.577464788732</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.230769230769</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="F21" s="17">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G21" s="17">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.8</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I21" s="17">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="J21" s="17">
-        <v>620</v>
+        <v>689</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.258064516129</v>
+        <v>-23.367198838897</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.581081081081</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="M21" s="18">
-        <v>15.311004784689</v>
+        <v>15.789473684210</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.098976109215</v>
+        <v>-66.708701134930</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M22" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
+        <v>19</v>
+      </c>
+      <c r="G23" s="14">
         <v>16</v>
       </c>
-      <c r="G23" s="14">
-        <v>17</v>
-      </c>
       <c r="H23" s="15">
-        <v>-5.882352941176</v>
+        <v>18.75</v>
       </c>
       <c r="I23" s="14">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J23" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K23" s="15">
-        <v>6.976744186046</v>
+        <v>6.122448979591</v>
       </c>
       <c r="L23" s="15">
-        <v>-16.363636363636</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="M23" s="15">
-        <v>9.523809523809</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E24" s="15">
-        <v>29.729729729729</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="F24" s="14">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G24" s="14">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.459459459459</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="I24" s="14">
-        <v>363</v>
+        <v>400</v>
       </c>
       <c r="J24" s="14">
-        <v>449</v>
+        <v>491</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.153674832962</v>
+        <v>-18.533604887983</v>
       </c>
       <c r="L24" s="15">
-        <v>2.542372881355</v>
+        <v>-1.234567901234</v>
       </c>
       <c r="M24" s="15">
-        <v>35.447761194029</v>
+        <v>37.457044673539</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>88.888888888888</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G25" s="14">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.986301369863</v>
+        <v>-23.214285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J25" s="14">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K25" s="15">
-        <v>-42.675159235668</v>
+        <v>-40.606060606060</v>
       </c>
       <c r="L25" s="15">
-        <v>-21.052631578947</v>
+        <v>-30</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E26" s="15">
-        <v>-38.709677419354</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G26" s="14">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H26" s="15">
-        <v>-14.285714285714</v>
+        <v>-27.083333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="J26" s="14">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="K26" s="15">
-        <v>3.174603174603</v>
+        <v>-2.764976958525</v>
       </c>
       <c r="L26" s="15">
-        <v>-20.081967213114</v>
+        <v>-21.851851851851</v>
       </c>
       <c r="M26" s="15">
-        <v>-32.055749128919</v>
+        <v>-33.855799373040</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="E27" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F27" s="14">
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
         <v>6</v>
       </c>
-      <c r="G27" s="14">
-        <v>8</v>
-      </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J27" s="14">
         <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L27" s="15">
-        <v>112.5</v>
+        <v>90</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
@@ -1444,22 +1444,22 @@
         <v>40</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>44.444444444444</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L28" s="15">
-        <v>-43.478260869565</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L29" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-20</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L30" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.818181818181</v>
+        <v>-84</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="L31" s="15">
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>76</v>

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14">
         <v>1</v>
@@ -899,7 +899,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -911,22 +911,22 @@
         <v>-60</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
         <v>15</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M15" s="15">
-        <v>71.428571428571</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N15" s="15">
-        <v>-25</v>
+        <v>-23.529411764705</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H16" s="15">
-        <v>-46.875</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="I16" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J16" s="14">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K16" s="15">
-        <v>-36.734693877551</v>
+        <v>-35.238095238095</v>
       </c>
       <c r="L16" s="15">
-        <v>-40.952380952380</v>
+        <v>-39.823008849557</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.416666666666</v>
+        <v>-35.238095238095</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.191536748329</v>
+        <v>-86.150712830957</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-37.5</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G17" s="14">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H17" s="15">
-        <v>-18.181818181818</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="J17" s="14">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="K17" s="15">
-        <v>2.515723270440</v>
+        <v>2.923976608187</v>
       </c>
       <c r="L17" s="15">
-        <v>15.602836879432</v>
+        <v>13.548387096774</v>
       </c>
       <c r="M17" s="15">
-        <v>40.517241379310</v>
+        <v>44.262295081967</v>
       </c>
       <c r="N17" s="15">
-        <v>-4.117647058823</v>
+        <v>-5.882352941176</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>6</v>
       </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
       <c r="E18" s="15">
-        <v>20</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J18" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.805970149253</v>
+        <v>-42.465753424657</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.052631578947</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.325581395348</v>
+        <v>-54.347826086956</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.285714285714</v>
+        <v>-89.285714285714</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="F19" s="14">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G19" s="14">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H19" s="15">
-        <v>-42.424242424242</v>
+        <v>-38</v>
       </c>
       <c r="I19" s="14">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="J19" s="14">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="K19" s="15">
-        <v>-33.469387755102</v>
+        <v>-33.210332103321</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.704433497536</v>
+        <v>-17.727272727272</v>
       </c>
       <c r="M19" s="15">
-        <v>53.773584905660</v>
+        <v>58.771929824561</v>
       </c>
       <c r="N19" s="15">
-        <v>1.875</v>
+        <v>4.624277456647</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-63.636363636363</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F20" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G20" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H20" s="15">
-        <v>-5.882352941176</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I20" s="14">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="J20" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K20" s="15">
-        <v>-14.705882352941</v>
+        <v>-15.315315315315</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.924528301886</v>
+        <v>-16.814159292035</v>
       </c>
       <c r="M20" s="15">
-        <v>97.727272727272</v>
+        <v>88</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.577464788732</v>
+        <v>-79.697624190064</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E21" s="18">
-        <v>-39.130434782608</v>
+        <v>-28.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="17">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.411764705882</v>
+        <v>-28.968253968254</v>
       </c>
       <c r="I21" s="17">
-        <v>528</v>
+        <v>574</v>
       </c>
       <c r="J21" s="17">
-        <v>689</v>
+        <v>749</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.367198838897</v>
+        <v>-23.364485981308</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.241379310344</v>
+        <v>-16.448326055313</v>
       </c>
       <c r="M21" s="18">
-        <v>15.789473684210</v>
+        <v>16.904276985743</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.708701134930</v>
+        <v>-66.992524439333</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
@@ -1207,13 +1207,13 @@
         <v>50</v>
       </c>
       <c r="L22" s="15">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15">
         <v>20</v>
       </c>
-      <c r="M22" s="15">
-        <v>50</v>
-      </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>18.75</v>
+        <v>35.294117647058</v>
       </c>
       <c r="I23" s="14">
+        <v>59</v>
+      </c>
+      <c r="J23" s="14">
         <v>52</v>
       </c>
-      <c r="J23" s="14">
-        <v>49</v>
-      </c>
       <c r="K23" s="15">
-        <v>6.122448979591</v>
+        <v>13.461538461538</v>
       </c>
       <c r="L23" s="15">
-        <v>-8.771929824561</v>
+        <v>-1.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>8.333333333333</v>
+        <v>22.916666666666</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D24" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.904761904761</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="G24" s="14">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.302325581395</v>
+        <v>7.975460122699</v>
       </c>
       <c r="I24" s="14">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="J24" s="14">
-        <v>491</v>
+        <v>536</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.533604887983</v>
+        <v>-16.417910447761</v>
       </c>
       <c r="L24" s="15">
-        <v>-1.234567901234</v>
+        <v>2.283105022831</v>
       </c>
       <c r="M24" s="15">
-        <v>37.457044673539</v>
+        <v>42.222222222222</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
         <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G25" s="14">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.214285714285</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I25" s="14">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="J25" s="14">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="K25" s="15">
-        <v>-40.606060606060</v>
+        <v>-36.416184971098</v>
       </c>
       <c r="L25" s="15">
-        <v>-30</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>-42.857142857142</v>
+        <v>15.789473684210</v>
       </c>
       <c r="F26" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G26" s="14">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H26" s="15">
-        <v>-27.083333333333</v>
+        <v>-20.618556701030</v>
       </c>
       <c r="I26" s="14">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="J26" s="14">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.764976958525</v>
+        <v>-2.542372881355</v>
       </c>
       <c r="L26" s="15">
-        <v>-21.851851851851</v>
+        <v>-19.580419580419</v>
       </c>
       <c r="M26" s="15">
-        <v>-33.855799373040</v>
+        <v>-32.551319648093</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>5</v>
       </c>
-      <c r="G27" s="14">
-        <v>6</v>
-      </c>
       <c r="H27" s="15">
-        <v>-16.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="14">
         <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>11.764705882352</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L27" s="15">
-        <v>90</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
+        <v>9</v>
+      </c>
+      <c r="G28" s="14">
         <v>7</v>
       </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
       <c r="H28" s="15">
-        <v>40</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>55.555555555555</v>
+        <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>-46.153846153846</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1476,31 +1476,31 @@
         <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M29" s="15">
         <v>-55.555555555555</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,31 +1517,31 @@
         <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-84</v>
+        <v>-86.206896551724</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,16 +1555,16 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
         <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,16 +1614,16 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>0</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>76</v>

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>4</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-75</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="I15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K15" s="15">
-        <v>-13.333333333333</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="L15" s="15">
-        <v>85.714285714285</v>
+        <v>75</v>
       </c>
       <c r="M15" s="15">
-        <v>85.714285714285</v>
+        <v>75</v>
       </c>
       <c r="N15" s="15">
-        <v>-23.529411764705</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H16" s="15">
-        <v>-37.931034482758</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J16" s="14">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.238095238095</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.823008849557</v>
+        <v>-40</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.238095238095</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.150712830957</v>
+        <v>-86.233269598470</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
         <v>60</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>-10</v>
       </c>
       <c r="I17" s="14">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="J17" s="14">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="K17" s="15">
-        <v>2.923976608187</v>
+        <v>4.278074866310</v>
       </c>
       <c r="L17" s="15">
-        <v>13.548387096774</v>
+        <v>18.902439024390</v>
       </c>
       <c r="M17" s="15">
-        <v>44.262295081967</v>
+        <v>48.854961832061</v>
       </c>
       <c r="N17" s="15">
-        <v>-5.882352941176</v>
+        <v>-3.940886699507</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-83.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-31.578947368421</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="I18" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.465753424657</v>
+        <v>-47.435897435897</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.153846153846</v>
+        <v>-48.101265822784</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.347826086956</v>
+        <v>-56.842105263157</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.285714285714</v>
+        <v>-90.531177829099</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>16</v>
+      </c>
+      <c r="D19" s="14">
         <v>17</v>
       </c>
-      <c r="D19" s="14">
-        <v>26</v>
-      </c>
       <c r="E19" s="15">
-        <v>-34.615384615384</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F19" s="14">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G19" s="14">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H19" s="15">
-        <v>-38</v>
+        <v>-27.835051546391</v>
       </c>
       <c r="I19" s="14">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="J19" s="14">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="K19" s="15">
-        <v>-33.210332103321</v>
+        <v>-30.902777777777</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.727272727272</v>
+        <v>-14.957264957265</v>
       </c>
       <c r="M19" s="15">
-        <v>58.771929824561</v>
+        <v>59.2</v>
       </c>
       <c r="N19" s="15">
-        <v>4.624277456647</v>
+        <v>2.577319587628</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-22.222222222222</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G20" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H20" s="15">
-        <v>-10.526315789473</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I20" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J20" s="14">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="K20" s="15">
-        <v>-15.315315315315</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.814159292035</v>
+        <v>-16.806722689075</v>
       </c>
       <c r="M20" s="15">
-        <v>88</v>
+        <v>90.384615384615</v>
       </c>
       <c r="N20" s="15">
-        <v>-79.697624190064</v>
+        <v>-80.588235294117</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,75 +1142,75 @@
         <v>43</v>
       </c>
       <c r="D21" s="17">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E21" s="18">
-        <v>-28.333333333333</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="F21" s="17">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G21" s="17">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.968253968254</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="I21" s="17">
-        <v>574</v>
+        <v>620</v>
       </c>
       <c r="J21" s="17">
-        <v>749</v>
+        <v>800</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.364485981308</v>
+        <v>-22.5</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.448326055313</v>
+        <v>-14.482758620689</v>
       </c>
       <c r="M21" s="18">
-        <v>16.904276985743</v>
+        <v>18.320610687022</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.992524439333</v>
+        <v>-67.402733964248</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="H22" s="15">
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>133.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>35.294117647058</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I23" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J23" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K23" s="15">
-        <v>13.461538461538</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L23" s="15">
-        <v>-1.666666666666</v>
+        <v>-1.538461538461</v>
       </c>
       <c r="M23" s="15">
-        <v>22.916666666666</v>
+        <v>28</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>6.666666666666</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="F24" s="14">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="G24" s="14">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H24" s="15">
-        <v>7.975460122699</v>
+        <v>2.547770700636</v>
       </c>
       <c r="I24" s="14">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="J24" s="14">
-        <v>536</v>
+        <v>569</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.417910447761</v>
+        <v>-16.344463971880</v>
       </c>
       <c r="L24" s="15">
-        <v>2.283105022831</v>
+        <v>2.807775377969</v>
       </c>
       <c r="M24" s="15">
-        <v>42.222222222222</v>
+        <v>42.089552238806</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F25" s="14">
         <v>46</v>
       </c>
       <c r="G25" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>21.052631578947</v>
+        <v>48.387096774193</v>
       </c>
       <c r="I25" s="14">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J25" s="14">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="K25" s="15">
-        <v>-36.416184971098</v>
+        <v>-33.519553072625</v>
       </c>
       <c r="L25" s="15">
-        <v>-29.032258064516</v>
+        <v>-28.742514970059</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E26" s="15">
-        <v>15.789473684210</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G26" s="14">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H26" s="15">
-        <v>-20.618556701030</v>
+        <v>-21.904761904761</v>
       </c>
       <c r="I26" s="14">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="J26" s="14">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.542372881355</v>
+        <v>-2.661596958174</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.580419580419</v>
+        <v>-16.065573770491</v>
       </c>
       <c r="M26" s="15">
-        <v>-32.551319648093</v>
+        <v>-30.997304582210</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>4</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-75</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I27" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K27" s="15">
-        <v>17.647058823529</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,10 +1426,10 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
@@ -1438,22 +1438,22 @@
         <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>28.571428571428</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>46.153846153846</v>
       </c>
       <c r="L28" s="15">
-        <v>-35.714285714285</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,32 +1475,32 @@
       <c r="E29" s="15">
         <v>-100</v>
       </c>
-      <c r="F29" s="14">
-        <v>2</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L29" s="15">
         <v>-55.555555555555</v>
       </c>
       <c r="M29" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-87.5</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,32 +1516,32 @@
       <c r="E30" s="15">
         <v>-100</v>
       </c>
-      <c r="F30" s="14">
-        <v>2</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L30" s="15">
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.206896551724</v>
+        <v>-87.096774193548</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1626,16 +1626,16 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>4</v>
-      </c>
       <c r="E15" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
@@ -914,19 +914,19 @@
         <v>14</v>
       </c>
       <c r="J15" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K15" s="15">
-        <v>-26.315789473684</v>
+        <v>-30</v>
       </c>
       <c r="L15" s="15">
         <v>75</v>
       </c>
       <c r="M15" s="15">
-        <v>75</v>
+        <v>55.555555555555</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-36.363636363636</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H16" s="15">
-        <v>-42.857142857142</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="J16" s="14">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-26.548672566371</v>
       </c>
       <c r="L16" s="15">
-        <v>-40</v>
+        <v>-36.641221374045</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.714285714285</v>
+        <v>-31.404958677686</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.233269598470</v>
+        <v>-85.204991087344</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>12.5</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F17" s="14">
         <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H17" s="15">
-        <v>-10</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="I17" s="14">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="J17" s="14">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="K17" s="15">
-        <v>4.278074866310</v>
+        <v>1.470588235294</v>
       </c>
       <c r="L17" s="15">
-        <v>18.902439024390</v>
+        <v>16.949152542372</v>
       </c>
       <c r="M17" s="15">
-        <v>48.854961832061</v>
+        <v>44.755244755244</v>
       </c>
       <c r="N17" s="15">
-        <v>-3.940886699507</v>
+        <v>-7.174887892376</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>20</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
         <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-52.380952380952</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J18" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K18" s="15">
-        <v>-47.435897435897</v>
+        <v>-44.578313253012</v>
       </c>
       <c r="L18" s="15">
-        <v>-48.101265822784</v>
+        <v>-47.126436781609</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.842105263157</v>
+        <v>-55.339805825242</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.531177829099</v>
+        <v>-90.356394129979</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E19" s="15">
-        <v>-5.882352941176</v>
+        <v>-30</v>
       </c>
       <c r="F19" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G19" s="14">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H19" s="15">
-        <v>-27.835051546391</v>
+        <v>-25</v>
       </c>
       <c r="I19" s="14">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="J19" s="14">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="K19" s="15">
-        <v>-30.902777777777</v>
+        <v>-30.188679245283</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.957264957265</v>
+        <v>-9.387755102040</v>
       </c>
       <c r="M19" s="15">
-        <v>59.2</v>
+        <v>68.181818181818</v>
       </c>
       <c r="N19" s="15">
-        <v>2.577319587628</v>
+        <v>6.730769230769</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-16.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F20" s="14">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H20" s="15">
-        <v>-18.181818181818</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I20" s="14">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J20" s="14">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="K20" s="15">
-        <v>-15.384615384615</v>
+        <v>-18.253968253968</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.806722689075</v>
+        <v>-17.6</v>
       </c>
       <c r="M20" s="15">
-        <v>90.384615384615</v>
+        <v>83.928571428571</v>
       </c>
       <c r="N20" s="15">
-        <v>-80.588235294117</v>
+        <v>-80.996309963099</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D21" s="17">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.686274509803</v>
+        <v>-17.910447761194</v>
       </c>
       <c r="F21" s="17">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G21" s="17">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.530612244898</v>
+        <v>-24.291497975708</v>
       </c>
       <c r="I21" s="17">
-        <v>620</v>
+        <v>675</v>
       </c>
       <c r="J21" s="17">
-        <v>800</v>
+        <v>867</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.5</v>
+        <v>-22.145328719723</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.482758620689</v>
+        <v>-12.790697674418</v>
       </c>
       <c r="M21" s="18">
-        <v>18.320610687022</v>
+        <v>19.469026548672</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.402733964248</v>
+        <v>-67.137293086660</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L22" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="F23" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G23" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H23" s="15">
-        <v>22.222222222222</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I23" s="14">
+        <v>71</v>
+      </c>
+      <c r="J23" s="14">
         <v>64</v>
       </c>
-      <c r="J23" s="14">
-        <v>56</v>
-      </c>
       <c r="K23" s="15">
-        <v>14.285714285714</v>
+        <v>10.9375</v>
       </c>
       <c r="L23" s="15">
-        <v>-1.538461538461</v>
+        <v>1.428571428571</v>
       </c>
       <c r="M23" s="15">
-        <v>28</v>
+        <v>24.561403508771</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.030303030303</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="F24" s="14">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="G24" s="14">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H24" s="15">
-        <v>2.547770700636</v>
+        <v>-9.815950920245</v>
       </c>
       <c r="I24" s="14">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="J24" s="14">
-        <v>569</v>
+        <v>612</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.344463971880</v>
+        <v>-16.830065359477</v>
       </c>
       <c r="L24" s="15">
-        <v>2.807775377969</v>
+        <v>3.665987780040</v>
       </c>
       <c r="M24" s="15">
-        <v>42.089552238806</v>
+        <v>35.372340425531</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>16.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="F25" s="14">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H25" s="15">
-        <v>48.387096774193</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="I25" s="14">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J25" s="14">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.519553072625</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="L25" s="15">
-        <v>-28.742514970059</v>
+        <v>-29.378531073446</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G26" s="14">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H26" s="15">
-        <v>-21.904761904761</v>
+        <v>-17.346938775510</v>
       </c>
       <c r="I26" s="14">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="J26" s="14">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.661596958174</v>
+        <v>-4.181184668989</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.065573770491</v>
+        <v>-16.158536585365</v>
       </c>
       <c r="M26" s="15">
-        <v>-30.997304582210</v>
+        <v>-31.930693069306</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>4</v>
-      </c>
       <c r="E27" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
@@ -1406,10 +1406,10 @@
         <v>21</v>
       </c>
       <c r="J27" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="L27" s="15">
         <v>50</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>46.153846153846</v>
+        <v>40</v>
       </c>
       <c r="L28" s="15">
-        <v>-36.666666666666</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,10 +1488,10 @@
         <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K29" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
         <v>-55.555555555555</v>
@@ -1500,7 +1500,7 @@
         <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.235294117647</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,10 +1529,10 @@
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
         <v>-50</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.096774193548</v>
+        <v>-88.571428571428</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" s="15">
-        <v>-30</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="M15" s="15">
-        <v>55.555555555555</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-36.363636363636</v>
+        <v>-34.782608695652</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G16" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H16" s="15">
-        <v>-4.166666666666</v>
+        <v>23.809523809523</v>
       </c>
       <c r="I16" s="14">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J16" s="14">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K16" s="15">
-        <v>-26.548672566371</v>
+        <v>-25.210084033613</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.641221374045</v>
+        <v>-36.879432624113</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.404958677686</v>
+        <v>-31.538461538461</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.204991087344</v>
+        <v>-85.289256198347</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>-23.529411764705</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G17" s="14">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.475409836065</v>
+        <v>-10.606060606060</v>
       </c>
       <c r="I17" s="14">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="J17" s="14">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="K17" s="15">
-        <v>1.470588235294</v>
+        <v>-0.888888888888</v>
       </c>
       <c r="L17" s="15">
-        <v>16.949152542372</v>
+        <v>16.753926701570</v>
       </c>
       <c r="M17" s="15">
-        <v>44.755244755244</v>
+        <v>47.682119205298</v>
       </c>
       <c r="N17" s="15">
-        <v>-7.174887892376</v>
+        <v>-8.606557377049</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>20</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
         <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
+        <v>-36.842105263157</v>
+      </c>
+      <c r="I18" s="14">
+        <v>52</v>
+      </c>
+      <c r="J18" s="14">
+        <v>86</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-39.534883720930</v>
+      </c>
+      <c r="L18" s="15">
         <v>-42.857142857142</v>
       </c>
-      <c r="I18" s="14">
-        <v>46</v>
-      </c>
-      <c r="J18" s="14">
-        <v>83</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-44.578313253012</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-47.126436781609</v>
-      </c>
       <c r="M18" s="15">
-        <v>-55.339805825242</v>
+        <v>-53.982300884955</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.356394129979</v>
+        <v>-89.723320158102</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E19" s="15">
-        <v>-30</v>
+        <v>-65.625</v>
       </c>
       <c r="F19" s="14">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="G19" s="14">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H19" s="15">
-        <v>-25</v>
+        <v>-36.190476190476</v>
       </c>
       <c r="I19" s="14">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="J19" s="14">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="K19" s="15">
-        <v>-30.188679245283</v>
+        <v>-33.142857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.387755102040</v>
+        <v>-13.011152416356</v>
       </c>
       <c r="M19" s="15">
-        <v>68.181818181818</v>
+        <v>62.5</v>
       </c>
       <c r="N19" s="15">
-        <v>6.730769230769</v>
+        <v>6.849315068493</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H20" s="15">
-        <v>-42.857142857142</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J20" s="14">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.253968253968</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.6</v>
+        <v>-21.641791044776</v>
       </c>
       <c r="M20" s="15">
-        <v>83.928571428571</v>
+        <v>69.354838709677</v>
       </c>
       <c r="N20" s="15">
-        <v>-80.996309963099</v>
+        <v>-82.112436115843</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.910447761194</v>
+        <v>-40.579710144927</v>
       </c>
       <c r="F21" s="17">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G21" s="17">
         <v>247</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.291497975708</v>
+        <v>-24.696356275303</v>
       </c>
       <c r="I21" s="17">
-        <v>675</v>
+        <v>718</v>
       </c>
       <c r="J21" s="17">
-        <v>867</v>
+        <v>936</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.145328719723</v>
+        <v>-23.290598290598</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.790697674418</v>
+        <v>-14.011976047904</v>
       </c>
       <c r="M21" s="18">
-        <v>19.469026548672</v>
+        <v>17.320261437908</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.137293086660</v>
+        <v>-67.467149977344</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
@@ -1210,7 +1210,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>5</v>
+      </c>
+      <c r="D23" s="14">
         <v>7</v>
       </c>
-      <c r="D23" s="14">
-        <v>8</v>
-      </c>
       <c r="E23" s="15">
-        <v>-12.5</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F23" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G23" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H23" s="15">
-        <v>19.047619047619</v>
+        <v>4.545454545454</v>
       </c>
       <c r="I23" s="14">
+        <v>76</v>
+      </c>
+      <c r="J23" s="14">
         <v>71</v>
       </c>
-      <c r="J23" s="14">
-        <v>64</v>
-      </c>
       <c r="K23" s="15">
-        <v>10.9375</v>
+        <v>7.042253521126</v>
       </c>
       <c r="L23" s="15">
-        <v>1.428571428571</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>24.561403508771</v>
+        <v>20.634920634920</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>33</v>
       </c>
       <c r="D24" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E24" s="15">
-        <v>-23.255813953488</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="F24" s="14">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G24" s="14">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H24" s="15">
-        <v>-9.815950920245</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>509</v>
+        <v>542</v>
       </c>
       <c r="J24" s="14">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.830065359477</v>
+        <v>-16.998468606431</v>
       </c>
       <c r="L24" s="15">
-        <v>3.665987780040</v>
+        <v>6.066536203522</v>
       </c>
       <c r="M24" s="15">
-        <v>35.372340425531</v>
+        <v>36.523929471032</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.894736842105</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="I25" s="14">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J25" s="14">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.897435897435</v>
+        <v>-37.681159420289</v>
       </c>
       <c r="L25" s="15">
-        <v>-29.378531073446</v>
+        <v>-29.120879120879</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-29.166666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G26" s="14">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="H26" s="15">
-        <v>-17.346938775510</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="I26" s="14">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="J26" s="14">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.181184668989</v>
+        <v>-3.606557377049</v>
       </c>
       <c r="L26" s="15">
-        <v>-16.158536585365</v>
+        <v>-15.028901734104</v>
       </c>
       <c r="M26" s="15">
-        <v>-31.930693069306</v>
+        <v>-32.568807339449</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K27" s="15">
-        <v>-4.545454545454</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
+        <v>100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
-        <v>8</v>
-      </c>
-      <c r="G28" s="14">
-        <v>6</v>
-      </c>
-      <c r="H28" s="15">
-        <v>33.333333333333</v>
-      </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-32.258064516129</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1488,19 +1488,19 @@
         <v>4</v>
       </c>
       <c r="J29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L29" s="15">
         <v>-55.555555555555</v>
       </c>
       <c r="M29" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.473684210526</v>
+        <v>-90.697674418604</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1529,19 +1529,19 @@
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L30" s="15">
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.571428571428</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -896,37 +896,37 @@
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J15" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K15" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>87.5</v>
+        <v>77.777777777777</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>-34.782608695652</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-91.666666666666</v>
       </c>
       <c r="F16" s="14">
+        <v>22</v>
+      </c>
+      <c r="G16" s="14">
         <v>26</v>
       </c>
-      <c r="G16" s="14">
-        <v>21</v>
-      </c>
       <c r="H16" s="15">
-        <v>23.809523809523</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I16" s="14">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J16" s="14">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.210084033613</v>
+        <v>-30.534351145038</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.879432624113</v>
+        <v>-40.131578947368</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.538461538461</v>
+        <v>-35.915492957746</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.289256198347</v>
+        <v>-85.78125</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G17" s="14">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.606060606060</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I17" s="14">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="J17" s="14">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.888888888888</v>
+        <v>-0.836820083682</v>
       </c>
       <c r="L17" s="15">
-        <v>16.753926701570</v>
+        <v>16.176470588235</v>
       </c>
       <c r="M17" s="15">
-        <v>47.682119205298</v>
+        <v>49.056603773584</v>
       </c>
       <c r="N17" s="15">
-        <v>-8.606557377049</v>
+        <v>-8.139534883720</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-36.842105263157</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J18" s="14">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="K18" s="15">
-        <v>-39.534883720930</v>
+        <v>-44.210526315789</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.857142857142</v>
+        <v>-43.617021276595</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.982300884955</v>
+        <v>-55.462184873949</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.723320158102</v>
+        <v>-90.185185185185</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15">
-        <v>-65.625</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G19" s="14">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H19" s="15">
-        <v>-36.190476190476</v>
+        <v>-34.343434343434</v>
       </c>
       <c r="I19" s="14">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="J19" s="14">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="K19" s="15">
-        <v>-33.142857142857</v>
+        <v>-32.702702702702</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.011152416356</v>
+        <v>-11.387900355871</v>
       </c>
       <c r="M19" s="15">
-        <v>62.5</v>
+        <v>56.603773584905</v>
       </c>
       <c r="N19" s="15">
-        <v>6.849315068493</v>
+        <v>5.508474576271</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H20" s="15">
-        <v>-36.666666666666</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I20" s="14">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J20" s="14">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="K20" s="15">
-        <v>-20.454545454545</v>
+        <v>-22.068965517241</v>
       </c>
       <c r="L20" s="15">
-        <v>-21.641791044776</v>
+        <v>-22.068965517241</v>
       </c>
       <c r="M20" s="15">
-        <v>69.354838709677</v>
+        <v>73.846153846153</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.112436115843</v>
+        <v>-81.803542673107</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E21" s="18">
-        <v>-40.579710144927</v>
+        <v>-46.478873239436</v>
       </c>
       <c r="F21" s="17">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G21" s="17">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.696356275303</v>
+        <v>-29.069767441860</v>
       </c>
       <c r="I21" s="17">
-        <v>718</v>
+        <v>759</v>
       </c>
       <c r="J21" s="17">
-        <v>936</v>
+        <v>1007</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.290598290598</v>
+        <v>-24.627606752730</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.011976047904</v>
+        <v>-14.334085778781</v>
       </c>
       <c r="M21" s="18">
-        <v>17.320261437908</v>
+        <v>15.701219512195</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.467149977344</v>
+        <v>-67.605633802816</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,13 +1221,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-28.571428571428</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
         <v>23</v>
@@ -1239,19 +1239,19 @@
         <v>4.545454545454</v>
       </c>
       <c r="I23" s="14">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J23" s="14">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K23" s="15">
-        <v>7.042253521126</v>
+        <v>10.810810810810</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-2.380952380952</v>
       </c>
       <c r="M23" s="15">
-        <v>20.634920634920</v>
+        <v>20.588235294117</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E24" s="15">
-        <v>-19.512195121951</v>
+        <v>-43.137254901960</v>
       </c>
       <c r="F24" s="14">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="G24" s="14">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.111111111111</v>
+        <v>-24.404761904761</v>
       </c>
       <c r="I24" s="14">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="J24" s="14">
-        <v>653</v>
+        <v>704</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.998468606431</v>
+        <v>-18.75</v>
       </c>
       <c r="L24" s="15">
-        <v>6.066536203522</v>
+        <v>4.954128440366</v>
       </c>
       <c r="M24" s="15">
-        <v>36.523929471032</v>
+        <v>32.407407407407</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G25" s="14">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>-26.190476190476</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="I25" s="14">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="J25" s="14">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="K25" s="15">
-        <v>-37.681159420289</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="L25" s="15">
-        <v>-29.120879120879</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
+        <v>80</v>
+      </c>
+      <c r="G26" s="14">
         <v>86</v>
       </c>
-      <c r="G26" s="14">
-        <v>88</v>
-      </c>
       <c r="H26" s="15">
-        <v>-2.272727272727</v>
+        <v>-6.976744186046</v>
       </c>
       <c r="I26" s="14">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="J26" s="14">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.606557377049</v>
+        <v>-4.037267080745</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.028901734104</v>
+        <v>-15.573770491803</v>
       </c>
       <c r="M26" s="15">
-        <v>-32.568807339449</v>
+        <v>-33.405172413793</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K27" s="15">
-        <v>-4.347826086956</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L27" s="15">
-        <v>37.5</v>
+        <v>35.294117647058</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>37.5</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>-37.142857142857</v>
+        <v>-42.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1497,10 +1497,10 @@
         <v>-55.555555555555</v>
       </c>
       <c r="M29" s="15">
-        <v>-63.636363636363</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.697674418604</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-90.243902439024</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,46 +869,46 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>3</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-66.666666666666</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
         <v>16</v>
@@ -920,13 +920,13 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>77.777777777777</v>
+        <v>60</v>
       </c>
       <c r="M15" s="15">
         <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>-91.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-15.384615384615</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J16" s="14">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="K16" s="15">
-        <v>-30.534351145038</v>
+        <v>-31.914893617021</v>
       </c>
       <c r="L16" s="15">
-        <v>-40.131578947368</v>
+        <v>-40</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.915492957746</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.78125</v>
+        <v>-85.628742514970</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G17" s="14">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.764705882352</v>
+        <v>-14.516129032258</v>
       </c>
       <c r="I17" s="14">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J17" s="14">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.836820083682</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>16.176470588235</v>
+        <v>13.181818181818</v>
       </c>
       <c r="M17" s="15">
-        <v>49.056603773584</v>
+        <v>47.337278106508</v>
       </c>
       <c r="N17" s="15">
-        <v>-8.139534883720</v>
+        <v>-10.431654676259</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-88.888888888888</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H18" s="15">
-        <v>-40.909090909090</v>
+        <v>-36</v>
       </c>
       <c r="I18" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J18" s="14">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K18" s="15">
-        <v>-44.210526315789</v>
+        <v>-45.631067961165</v>
       </c>
       <c r="L18" s="15">
-        <v>-43.617021276595</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.462184873949</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.185185185185</v>
+        <v>-90.443686006825</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19" s="14">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H19" s="15">
-        <v>-34.343434343434</v>
+        <v>-35.922330097087</v>
       </c>
       <c r="I19" s="14">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="J19" s="14">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="K19" s="15">
-        <v>-32.702702702702</v>
+        <v>-31.713554987212</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.387900355871</v>
+        <v>-12.171052631578</v>
       </c>
       <c r="M19" s="15">
-        <v>56.603773584905</v>
+        <v>56.140350877193</v>
       </c>
       <c r="N19" s="15">
-        <v>5.508474576271</v>
+        <v>4.705882352941</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-38.461538461538</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H20" s="15">
-        <v>-41.176470588235</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J20" s="14">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K20" s="15">
-        <v>-22.068965517241</v>
+        <v>-21.710526315789</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.068965517241</v>
+        <v>-20.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>73.846153846153</v>
+        <v>65.277777777777</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.803542673107</v>
+        <v>-81.720430107526</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E21" s="18">
-        <v>-46.478873239436</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
         <v>183</v>
       </c>
       <c r="G21" s="17">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.069767441860</v>
+        <v>-30.418250950570</v>
       </c>
       <c r="I21" s="17">
-        <v>759</v>
+        <v>804</v>
       </c>
       <c r="J21" s="17">
-        <v>1007</v>
+        <v>1063</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.627606752730</v>
+        <v>-24.365004703668</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.334085778781</v>
+        <v>-14.830508474576</v>
       </c>
       <c r="M21" s="18">
-        <v>15.701219512195</v>
+        <v>14.529914529914</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.605633802816</v>
+        <v>-67.684887459807</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1191,26 +1191,26 @@
       <c r="F22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-80</v>
       </c>
       <c r="F23" s="14">
+        <v>19</v>
+      </c>
+      <c r="G23" s="14">
         <v>23</v>
       </c>
-      <c r="G23" s="14">
-        <v>22</v>
-      </c>
       <c r="H23" s="15">
-        <v>4.545454545454</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I23" s="14">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J23" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K23" s="15">
-        <v>10.810810810810</v>
+        <v>5.063291139240</v>
       </c>
       <c r="L23" s="15">
-        <v>-2.380952380952</v>
+        <v>-3.488372093023</v>
       </c>
       <c r="M23" s="15">
-        <v>20.588235294117</v>
+        <v>20.289855072463</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D24" s="14">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E24" s="15">
-        <v>-43.137254901960</v>
+        <v>5.128205128205</v>
       </c>
       <c r="F24" s="14">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G24" s="14">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.404761904761</v>
+        <v>-21.264367816092</v>
       </c>
       <c r="I24" s="14">
-        <v>572</v>
+        <v>614</v>
       </c>
       <c r="J24" s="14">
-        <v>704</v>
+        <v>743</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.75</v>
+        <v>-17.362045760430</v>
       </c>
       <c r="L24" s="15">
-        <v>4.954128440366</v>
+        <v>7.155322862129</v>
       </c>
       <c r="M24" s="15">
-        <v>32.407407407407</v>
+        <v>32.900432900432</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-58.823529411764</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>-52.941176470588</v>
+        <v>-51.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="J25" s="14">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="K25" s="15">
-        <v>-39.285714285714</v>
+        <v>-38.075313807531</v>
       </c>
       <c r="L25" s="15">
-        <v>-29.166666666666</v>
+        <v>-25.628140703517</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
         <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>29.411764705882</v>
       </c>
       <c r="F26" s="14">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G26" s="14">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.976744186046</v>
+        <v>-3.947368421052</v>
       </c>
       <c r="I26" s="14">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="J26" s="14">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.037267080745</v>
+        <v>-2.359882005899</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.573770491803</v>
+        <v>-13.802083333333</v>
       </c>
       <c r="M26" s="15">
-        <v>-33.405172413793</v>
+        <v>-33.266129032258</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,20 +1384,20 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>3</v>
-      </c>
       <c r="E27" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
         <v>-66.666666666666</v>
@@ -1406,13 +1406,13 @@
         <v>23</v>
       </c>
       <c r="J27" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K27" s="15">
-        <v>-11.538461538461</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L27" s="15">
-        <v>35.294117647058</v>
+        <v>27.777777777777</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,10 +1429,10 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>5</v>
@@ -1447,13 +1447,13 @@
         <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>27.777777777777</v>
+        <v>21.052631578947</v>
       </c>
       <c r="L28" s="15">
-        <v>-42.5</v>
+        <v>-43.902439024390</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1500,7 +1500,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1541,7 +1541,7 @@
         <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.243902439024</v>
+        <v>-90.697674418604</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-043pct.xlsx
+++ b/data/source/weekly/cs-en-us-043pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -851,351 +851,351 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
+        <v>-75</v>
+      </c>
+      <c r="L14" s="15">
         <v>-66.666666666666</v>
-      </c>
-      <c r="L14" s="15">
-        <v>-50</v>
       </c>
       <c r="M14" s="15">
         <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-96</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L15" s="15">
-        <v>60</v>
+        <v>63.636363636363</v>
       </c>
       <c r="M15" s="15">
-        <v>60</v>
+        <v>63.636363636363</v>
       </c>
       <c r="N15" s="15">
-        <v>-36</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H16" s="15">
-        <v>-27.272727272727</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="I16" s="14">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J16" s="14">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="K16" s="15">
-        <v>-31.914893617021</v>
+        <v>-33.774834437086</v>
       </c>
       <c r="L16" s="15">
-        <v>-40</v>
+        <v>-42.528735632183</v>
       </c>
       <c r="M16" s="15">
-        <v>-36.842105263157</v>
+        <v>-37.106918238993</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.628742514970</v>
+        <v>-85.935302390998</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
         <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F17" s="14">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G17" s="14">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.516129032258</v>
+        <v>-12.962962962963</v>
       </c>
       <c r="I17" s="14">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="J17" s="14">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="K17" s="15">
         <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>13.181818181818</v>
+        <v>7.949790794979</v>
       </c>
       <c r="M17" s="15">
-        <v>47.337278106508</v>
+        <v>47.428571428571</v>
       </c>
       <c r="N17" s="15">
-        <v>-10.431654676259</v>
+        <v>-12.244897959183</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H18" s="15">
-        <v>-36</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I18" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J18" s="14">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K18" s="15">
-        <v>-45.631067961165</v>
+        <v>-45.871559633027</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.857142857142</v>
+        <v>-44.339622641509</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.555555555555</v>
+        <v>-54.263565891472</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.443686006825</v>
+        <v>-90.694006309148</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
+        <v>14</v>
+      </c>
+      <c r="D19" s="14">
         <v>18</v>
       </c>
-      <c r="D19" s="14">
-        <v>21</v>
-      </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H19" s="15">
-        <v>-35.922330097087</v>
+        <v>-37.362637362637</v>
       </c>
       <c r="I19" s="14">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="J19" s="14">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="K19" s="15">
-        <v>-31.713554987212</v>
+        <v>-31.540342298288</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.171052631578</v>
+        <v>-11.671924290220</v>
       </c>
       <c r="M19" s="15">
-        <v>56.140350877193</v>
+        <v>48.936170212766</v>
       </c>
       <c r="N19" s="15">
-        <v>4.705882352941</v>
+        <v>3.703703703703</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
         <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
         <v>35</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>-34.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J20" s="14">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="K20" s="15">
-        <v>-21.710526315789</v>
+        <v>-22.360248447205</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.666666666666</v>
+        <v>-22.360248447205</v>
       </c>
       <c r="M20" s="15">
-        <v>65.277777777777</v>
+        <v>58.227848101265</v>
       </c>
       <c r="N20" s="15">
-        <v>-81.720430107526</v>
+        <v>-81.751824817518</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-32.727272727272</v>
       </c>
       <c r="F21" s="17">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="G21" s="17">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.418250950570</v>
+        <v>-35.856573705179</v>
       </c>
       <c r="I21" s="17">
-        <v>804</v>
+        <v>841</v>
       </c>
       <c r="J21" s="17">
-        <v>1063</v>
+        <v>1118</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.365004703668</v>
+        <v>-24.776386404293</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.830508474576</v>
+        <v>-16.815034619188</v>
       </c>
       <c r="M21" s="18">
-        <v>14.529914529914</v>
+        <v>13.189771197846</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.684887459807</v>
+        <v>-68.204158790170</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="14">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I22" s="14">
         <v>9</v>
@@ -1207,13 +1207,13 @@
         <v>80</v>
       </c>
       <c r="L22" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="M22" s="15">
         <v>12.5</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-80</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H23" s="15">
-        <v>-17.391304347826</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I23" s="14">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J23" s="14">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K23" s="15">
-        <v>5.063291139240</v>
+        <v>3.658536585365</v>
       </c>
       <c r="L23" s="15">
-        <v>-3.488372093023</v>
+        <v>-8.602150537634</v>
       </c>
       <c r="M23" s="15">
-        <v>20.289855072463</v>
+        <v>16.438356164383</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>5.128205128205</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G24" s="14">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="H24" s="15">
-        <v>-21.264367816092</v>
+        <v>-16.455696202531</v>
       </c>
       <c r="I24" s="14">
-        <v>614</v>
+        <v>643</v>
       </c>
       <c r="J24" s="14">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.362045760430</v>
+        <v>-16.493506493506</v>
       </c>
       <c r="L24" s="15">
-        <v>7.155322862129</v>
+        <v>5.930807248764</v>
       </c>
       <c r="M24" s="15">
-        <v>32.900432900432</v>
+        <v>28.6</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-20</v>
+        <v>40</v>
       </c>
       <c r="F25" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H25" s="15">
-        <v>-51.666666666666</v>
+        <v>-38.775510204081</v>
       </c>
       <c r="I25" s="14">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="J25" s="14">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K25" s="15">
-        <v>-38.075313807531</v>
+        <v>-36.475409836065</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.628140703517</v>
+        <v>-26.886792452830</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>11</v>
+      </c>
+      <c r="D26" s="14">
         <v>22</v>
       </c>
-      <c r="D26" s="14">
-        <v>17</v>
-      </c>
       <c r="E26" s="15">
-        <v>29.411764705882</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G26" s="14">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.947368421052</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="I26" s="14">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="J26" s="14">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.359882005899</v>
+        <v>-5.817174515235</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.802083333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>-33.266129032258</v>
+        <v>-36.802973977695</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I27" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J27" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.814814814814</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L27" s="15">
-        <v>27.777777777777</v>
+        <v>31.578947368421</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,122 +1426,122 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>75</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J28" s="14">
         <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>21.052631578947</v>
+        <v>36.842105263157</v>
       </c>
       <c r="L28" s="15">
-        <v>-43.902439024390</v>
+        <v>-39.534883720930</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L29" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.304347826087</v>
+        <v>-89.795918367346</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
         <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>-55.555555555555</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="M30" s="15">
-        <v>-60</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.697674418604</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L31" s="15">
         <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
@@ -1638,10 +1638,10 @@
         <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>76</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>2109</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>1083</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1974</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>971</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>3237</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>9500</v>
